--- a/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
+++ b/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:37:22+05:30</t>
+    <t>2026-08-31T12:11:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
+++ b/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T12:11:16+00:00</t>
+    <t>2026-09-02T05:31:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
+++ b/docs/CodeSystem-DIPSVitalSignsObservationPrePostduktal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T05:31:41+00:00</t>
+    <t>2026-09-03T11:16:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
